--- a/currentbuild/StructureDefinition-lmdi-administrert-ved.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-administrert-ved.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:50:47+00:00</t>
+    <t>2026-10-20T08:54:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
